--- a/public/SubTracker_Import_Template.xlsx
+++ b/public/SubTracker_Import_Template.xlsx
@@ -463,11 +463,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Company Name</v>
+  <dimension ref="A1:R1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Company Name*</v>
       </c>
       <c r="B1" t="str">
         <v>Trade</v>
@@ -482,21 +482,48 @@
         <v>Phone</v>
       </c>
       <c r="F1" t="str">
+        <v>Address 1</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Address 2</v>
+      </c>
+      <c r="H1" t="str">
+        <v>City</v>
+      </c>
+      <c r="I1" t="str">
+        <v>State</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Zip Code</v>
+      </c>
+      <c r="K1" t="str">
+        <v>NJ PWC #</v>
+      </c>
+      <c r="L1" t="str">
+        <v>NJ BRC #</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Sage ERP ID</v>
+      </c>
+      <c r="N1" t="str">
+        <v>BRC Name Control</v>
+      </c>
+      <c r="O1" t="str">
         <v>Notes</v>
       </c>
-      <c r="G1" t="str">
+      <c r="P1" t="str">
         <v>External ID</v>
       </c>
-      <c r="H1" t="str">
+      <c r="Q1" t="str">
         <v>Legacy ID</v>
       </c>
-      <c r="I1" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+      <c r="R1" t="str">
+        <v>Active*</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:R1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/SubTracker_Import_Template.xlsx
+++ b/public/SubTracker_Import_Template.xlsx
@@ -72,8 +72,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -432,9 +433,14 @@
         <v>Date columns accept Excel dates (MM/DD/YYYY).</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Taxpayer ID (FEIN) is optional and stored as text; enter 001234567 or 12-3456789. Do not append zeros.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -463,7 +469,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:S1"/>
+  <cols>
+    <col min="14" max="14" width="22" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -503,27 +512,30 @@
         <v>NJ BRC #</v>
       </c>
       <c r="M1" t="str">
+        <v>BRC Name Control</v>
+      </c>
+      <c r="N1" s="1" t="str">
+        <v>Taxpayer ID (FEIN)</v>
+      </c>
+      <c r="O1" t="str">
         <v>Sage ERP ID</v>
       </c>
-      <c r="N1" t="str">
-        <v>BRC Name Control</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Notes</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>External ID</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Legacy ID</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Active*</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/SubTracker_Import_Template.xlsx
+++ b/public/SubTracker_Import_Template.xlsx
@@ -8,10 +8,9 @@
     <sheet name="Contractors" sheetId="3" r:id="rId3"/>
     <sheet name="Project Assignments" sheetId="4" r:id="rId4"/>
     <sheet name="Compliance Records" sheetId="5" r:id="rId5"/>
-    <sheet name="Insurance" sheetId="6" r:id="rId6"/>
-    <sheet name="Tiered Subs" sheetId="7" r:id="rId7"/>
-    <sheet name="Follow-Ups" sheetId="8" r:id="rId8"/>
-    <sheet name="_Lists" sheetId="9" r:id="rId9"/>
+    <sheet name="Tiered Subs" sheetId="6" r:id="rId6"/>
+    <sheet name="Follow-Ups" sheetId="7" r:id="rId7"/>
+    <sheet name="_Lists" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -406,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -420,27 +419,37 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Supported worksheets: Projects, Contractors, Project Assignments, Compliance Records, Insurance, Tiered Subs, Follow-Ups.</v>
+        <v>Supported worksheets: Projects, Contractors, Project Assignments, Compliance Records, Tiered Subs, Follow-Ups.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Yes/No columns accept Yes or No.</v>
+        <v>Manual Insurance and Certificate Of Insurance tracking are retired. Use the reviewed myCOI workflow for insurance.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Date columns accept Excel dates (MM/DD/YYYY).</v>
+        <v>Project Assignments controls MANUAL ownership only; it cannot remove MYCOI ownership.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>Yes/No columns accept Yes or No.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Date columns accept Excel dates (MM/DD/YYYY).</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>Taxpayer ID (FEIN) is optional and stored as text; enter 001234567 or 12-3456789. Do not append zeros.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -613,37 +622,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Company Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>COI On File</v>
-      </c>
-      <c r="C1" t="str">
-        <v>General Liability On File</v>
-      </c>
-      <c r="D1" t="str">
-        <v>General Liability Expiration Date</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Workers Comp On File</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Workers Comp Expiration Date</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1"/>
   <sheetData>
     <row r="1">
@@ -667,7 +645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G1"/>
   <sheetData>
@@ -701,7 +679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D7"/>
   <sheetData>
